--- a/request_forms/015_cards_design_request--request_forms.xlsx
+++ b/request_forms/015_cards_design_request--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -947,8 +947,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -976,12 +976,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'business_card',_'value':_'business'}</t>
+          <t>business_card</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Business Card', 'value': 'business'}</t>
+          <t>Business Card</t>
         </is>
       </c>
     </row>
@@ -993,12 +993,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'greeting_card',_'value':_'greeting'}</t>
+          <t>greeting_card</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Greeting Card', 'value': 'greeting'}</t>
+          <t>Greeting Card</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'thank_you_card',_'value':_'thank_you'}</t>
+          <t>thank_you_card</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Thank You Card', 'value': 'thank_you'}</t>
+          <t>Thank You Card</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'postcard',_'value':_'postcard'}</t>
+          <t>postcard</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Postcard', 'value': 'postcard'}</t>
+          <t>Postcard</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'custom_request',_'value':_'custom'}</t>
+          <t>custom_request</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Custom Request', 'value': 'custom'}</t>
+          <t>Custom Request</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'standard_(3.5_x_2)',_'value':_'standard'}</t>
+          <t>standard_(3.5_x_2)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Standard (3.5 x 2)', 'value': 'standard'}</t>
+          <t>Standard (3.5 x 2)</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'square_(2.5_x_2.5)',_'value':_'square'}</t>
+          <t>square_(2.5_x_2.5)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Square (2.5 x 2.5)', 'value': 'square'}</t>
+          <t>Square (2.5 x 2.5)</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'a7_(5.25_x_7.25)',_'value':_'a7'}</t>
+          <t>a7_(5.25_x_7.25)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'A7 (5.25 x 7.25)', 'value': 'a7'}</t>
+          <t>A7 (5.25 x 7.25)</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'custom_dimensions',_'value':_'custom'}</t>
+          <t>custom_dimensions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Custom Dimensions', 'value': 'custom'}</t>
+          <t>Custom Dimensions</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'horizontal_(landscape)',_'value':_'horizontal'}</t>
+          <t>horizontal_(landscape)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Horizontal (Landscape)', 'value': 'horizontal'}</t>
+          <t>Horizontal (Landscape)</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'vertical_(portrait)',_'value':_'vertical'}</t>
+          <t>vertical_(portrait)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Vertical (Portrait)', 'value': 'vertical'}</t>
+          <t>Vertical (Portrait)</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'premium_matte_(16pt)',_'value':_'matte'}</t>
+          <t>premium_matte_(16pt)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Premium Matte (16pt)', 'value': 'matte'}</t>
+          <t>Premium Matte (16pt)</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'high-gloss_(uv_coating)',_'value':_'gloss'}</t>
+          <t>high-gloss_(uv_coating)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'High-Gloss (UV Coating)', 'value': 'gloss'}</t>
+          <t>High-Gloss (UV Coating)</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'recycled_kraft',_'value':_'recycled'}</t>
+          <t>recycled_kraft</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Recycled Kraft', 'value': 'recycled'}</t>
+          <t>Recycled Kraft</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'pearl_(metallic)',_'value':_'pearl'}</t>
+          <t>pearl_(metallic)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Pearl (Metallic)', 'value': 'pearl'}</t>
+          <t>Pearl (Metallic)</t>
         </is>
       </c>
     </row>
